--- a/data/trans_orig/P41C1_AOS_2023_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P41C1_AOS_2023_R-Edad-trans_orig.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en años que han tardado en que algún miembro de la pareja se quede embarazada</t>
+          <t>Tiempo medio en años que han tardado en que algún miembro de la pareja se quede embarazada (tasa de respuesta: 93,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +538,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>16-24</t>
+          <t>25-34</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,96</t>
         </is>
       </c>
     </row>
@@ -571,24 +571,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,25; 1,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,37; 2,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,56; 1,82</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>2,46</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>2,62</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>2,55</t>
         </is>
       </c>
     </row>
@@ -621,24 +621,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,0</t>
+          <t>1,61; 3,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,87</t>
+          <t>1,95; 3,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,81</t>
+          <t>2,03; 3,09</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,46</t>
+          <t>4,45</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,62</t>
+          <t>5,32</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,55</t>
+          <t>4,9</t>
         </is>
       </c>
     </row>
@@ -671,24 +671,24 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,2</t>
+          <t>2,6; 8,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,46</t>
+          <t>3,35; 8,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 3,13</t>
+          <t>3,42; 7,06</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4,45</t>
+          <t>2,89</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,32</t>
+          <t>3,5</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,9</t>
+          <t>3,2</t>
         </is>
       </c>
     </row>
@@ -721,238 +721,34 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,57; 7,6</t>
+          <t>1,93; 4,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 8,23</t>
+          <t>2,6; 5,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,93</t>
+          <t>2,47; 4,29</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>55-64</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>65-74</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>2,89</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>3,5</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>3,2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>1,98; 4,6</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2,56; 5,04</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2,45; 4,31</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="5">
     <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A14:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_orig/P41C1_AOS_2023_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P41C1_AOS_2023_R-Edad-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>1,0</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>0,92</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,9</t>
+          <t>0,27; 2,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,82</t>
+          <t>0,52; 1,79</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,46</t>
+          <t>2,72</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>2,54</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>2,62</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,55</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,16</t>
+          <t>1,92; 3,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,49</t>
+          <t>1,88; 3,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,09</t>
+          <t>2,1; 3,14</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4,45</t>
+          <t>4,39</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5,32</t>
+          <t>5,39</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,9</t>
+          <t>4,91</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 8,22</t>
+          <t>2,48; 7,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,35; 8,12</t>
+          <t>3,4; 8,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 7,06</t>
+          <t>3,33; 6,95</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,89</t>
+          <t>2,93</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,5</t>
+          <t>3,39</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,2</t>
+          <t>3,17</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,76</t>
+          <t>2,03; 4,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 5,07</t>
+          <t>2,41; 4,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 4,29</t>
+          <t>2,5; 4,3</t>
         </is>
       </c>
     </row>
